--- a/data/trans_orig/P1435-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1435-Habitat-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2007</t>
+          <t>Población con diagnóstico de dolor menstrual en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39278</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>27563</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>19663</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>39278</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>660788</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>648980</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>669247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649073</t>
+          <t>648980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668688</t>
+          <t>669247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>660788</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>649073</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>668688</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>696</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688351</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>688351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1013,41 +883,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>688351</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>688351</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>688351</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1066,37 +901,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48527</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36414</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65586</t>
+          <t>63077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>48527</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>36414</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>65586</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1179,37 +979,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>863</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>919866</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>905316</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>932074</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>902807</t>
+          <t>905316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>931979</t>
+          <t>932074</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,47 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>919866</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>902807</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>931979</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>908</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>968393</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>968393</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>968393</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1356,41 +1121,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>968393</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>968393</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>968393</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1409,37 +1139,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82149</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66246</t>
+          <t>66546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98732</t>
+          <t>99958</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>82149</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>66246</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>98732</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>12,01%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>14,44%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1522,37 +1217,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>601692</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>583883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>617295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>585109</t>
+          <t>583883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>617595</t>
+          <t>617295</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>601692</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>585109</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>617595</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>87,99%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>85,56%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -1635,37 +1295,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>696</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,41 +1359,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>683841</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>683841</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>683841</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1752,37 +1377,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101907</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123458</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80679</t>
+          <t>84883</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120414</t>
+          <t>123458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>101907</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>80679</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>120414</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1455,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>898</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>936705</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>915154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>953729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>918198</t>
+          <t>915154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>957933</t>
+          <t>953729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>936705</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>918198</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>957933</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>90,19%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>88,41%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1533,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>997</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1038612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1038612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1038612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2042,41 +1597,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>997</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1038612</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1038612</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1038612</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2095,37 +1615,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260146</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>229865</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234160</t>
+          <t>229865</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>293836</t>
+          <t>290809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>260146</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>234160</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>293836</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>7,7%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -2208,37 +1693,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3119051</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3088388</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3149332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3085361</t>
+          <t>3088388</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3145037</t>
+          <t>3149332</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3119051</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3085361</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3145037</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>92,3%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
+          <t>93,2%</t>
         </is>
       </c>
     </row>
@@ -2321,37 +1771,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3379197</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3379197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3379197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2385,41 +1835,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2433,14 +1848,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2454,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2473,25 +1887,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2012</t>
+          <t>Población con diagnóstico de dolor menstrual en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +1909,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2511,17 +1918,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2592,41 +1988,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2649,13 +2010,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2670,37 +2024,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23793</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35117</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,47 +2084,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>23793</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>15064</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>35117</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -2783,37 +2102,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>627</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>673257</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>661800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>681230</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661933</t>
+          <t>661800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681986</t>
+          <t>681230</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,47 +2162,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>673257</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>661933</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>681986</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -2896,37 +2180,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>697050</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>697050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>697050</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2960,41 +2244,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>697050</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>697050</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>697050</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3013,37 +2262,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25338</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48534</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,47 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>35122</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>25338</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>48534</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -3126,37 +2340,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>904</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>993851</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>980862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1005175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>980439</t>
+          <t>980862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1003635</t>
+          <t>1005175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,47 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>904</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>993851</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>980439</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1003635</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -3239,37 +2418,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>938</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1028973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1028973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1028973</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3303,41 +2482,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1028973</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1028973</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1028973</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3356,37 +2500,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42323</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55445</t>
+          <t>57459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,47 +2560,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>42323</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>29830</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>55445</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -3469,37 +2578,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>664</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>734851</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>719715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>745618</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>721729</t>
+          <t>719715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>747344</t>
+          <t>745618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,47 +2638,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>734851</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>721729</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>747344</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -3582,37 +2656,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>777174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>777174</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>777174</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3646,41 +2720,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>777174</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>777174</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>777174</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3699,37 +2738,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50707</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>25655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49028</t>
+          <t>50707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,47 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>36171</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>25339</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>49028</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -3812,37 +2816,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>968</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1015730</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1001194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1026246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002873</t>
+          <t>1001194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1026562</t>
+          <t>1026246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,47 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1015730</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1002873</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1026562</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -3925,37 +2894,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1051901</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1051901</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1051901</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3989,41 +2958,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1051901</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1051901</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1051901</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4042,37 +2976,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>137409</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115321</t>
+          <t>116982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163263</t>
+          <t>162900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,47 +3036,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>137409</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>115321</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>163263</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -4155,37 +3054,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3417689</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3392198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3438116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3391835</t>
+          <t>3392198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3439777</t>
+          <t>3438116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,47 +3114,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3163</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3417689</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3391835</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3439777</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -4268,37 +3132,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3555098</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3555098</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3555098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4332,41 +3196,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3296</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3555098</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3555098</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3555098</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4380,14 +3209,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -4401,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4420,25 +3248,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2016</t>
+          <t>Población con diagnóstico de dolor menstrual en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +3270,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4458,17 +3279,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -4539,41 +3349,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -4596,13 +3371,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4617,37 +3385,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,47 +3445,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>8687</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>4463</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>16438</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -4730,37 +3463,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>657</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>664152</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>657292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>668621</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>656401</t>
+          <t>657292</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668376</t>
+          <t>668621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,47 +3523,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>664152</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>656401</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>668376</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -4843,37 +3541,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>666</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672839</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672839</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4907,41 +3605,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>672839</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>672839</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>672839</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4960,37 +3623,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,47 +3683,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>10409</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>5696</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>18932</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5073,37 +3701,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>966</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1032504</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1025051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1037406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1023981</t>
+          <t>1025051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1037217</t>
+          <t>1037406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,47 +3761,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1032504</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1023981</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1037217</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5186,37 +3779,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>977</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1042913</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1042913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1042913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5250,41 +3843,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1042913</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1042913</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1042913</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5303,37 +3861,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,47 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13059</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6867</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>22283</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -5416,37 +3939,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>723</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>771952</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>763493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>778237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>762728</t>
+          <t>763493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>778144</t>
+          <t>778237</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,47 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>771952</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>762728</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>778144</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -5529,37 +4017,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>736</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>785011</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>785011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>785011</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5593,41 +4081,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>785011</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>785011</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>785011</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5646,37 +4099,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34233</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,47 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>34233</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>24898</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>47902</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -5759,37 +4177,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>925</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1009546</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1020135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>995877</t>
+          <t>997372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1018881</t>
+          <t>1020135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,47 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1009546</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>995877</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1018881</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -5872,37 +4255,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>959</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1043779</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1043779</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1043779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5936,41 +4319,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1043779</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1043779</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1043779</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5989,37 +4337,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66388</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84756</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50301</t>
+          <t>52831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84274</t>
+          <t>84756</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,47 +4397,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>66388</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>50301</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>84274</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -6102,37 +4415,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3478154</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3459786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3491711</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3460268</t>
+          <t>3459786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3494241</t>
+          <t>3491711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,47 +4475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3478154</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3460268</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3494241</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -6215,37 +4493,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3544542</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3544542</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3544542</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6279,41 +4557,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3544542</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3544542</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3544542</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6327,14 +4570,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -6348,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6367,25 +4609,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor menstrual en 2023</t>
+          <t>Población con diagnóstico de dolor menstrual en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +4631,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6405,17 +4640,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -6486,41 +4710,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -6543,13 +4732,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -6564,37 +4746,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28625</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +4791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20176</t>
+          <t>19860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>41461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,47 +4806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>28625</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>20176</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>41357</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -6677,37 +4824,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>646745</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>633909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655510</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +4869,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>634013</t>
+          <t>633909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655194</t>
+          <t>655510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,47 +4884,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>646745</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>634013</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>655194</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>95,76%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -6790,37 +4902,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>675370</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>675370</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>675370</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6854,41 +4966,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>675370</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>675370</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>675370</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6907,37 +4984,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +5029,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40798</t>
+          <t>40478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67039</t>
+          <t>67201</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,47 +5044,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>52962</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>40798</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>67039</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -7020,37 +5062,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>901772</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>887533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>914256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +5107,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>887695</t>
+          <t>887533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>913936</t>
+          <t>914256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,47 +5122,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>901772</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>887695</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>913936</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>92,98%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -7133,37 +5140,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>954734</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>954734</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>954734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7197,41 +5204,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1512</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>954734</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>954734</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>954734</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7250,37 +5222,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +5267,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27468</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79816</t>
+          <t>78840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,47 +5282,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>54074</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>27468</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>79816</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -7363,37 +5300,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>975</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>875602</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>850836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>902196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +5345,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>849860</t>
+          <t>850836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>902208</t>
+          <t>902196</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,47 +5360,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>875602</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>849860</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>902208</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>91,41%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -7476,37 +5378,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>929676</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>929676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>929676</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7540,41 +5442,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>929676</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>929676</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>929676</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7593,37 +5460,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131165</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61349</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>330793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +5505,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61638</t>
+          <t>61349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>317036</t>
+          <t>330793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,47 +5520,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>131165</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>61638</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>317036</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>29,06%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -7706,37 +5538,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>959958</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1029774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +5583,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>774087</t>
+          <t>760330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029485</t>
+          <t>1029774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,47 +5598,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1480</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>959958</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>774087</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1029485</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>87,98%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>70,94%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -7819,37 +5616,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1091123</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1091123</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1091123</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7883,41 +5680,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1091123</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>1091123</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1091123</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7936,37 +5698,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266826</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>510642</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +5743,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187266</t>
+          <t>188999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>549979</t>
+          <t>510642</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,47 +5758,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>266826</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>187266</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>549979</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -8049,37 +5776,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3384078</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3140262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3461905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +5821,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3100925</t>
+          <t>3140262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3463638</t>
+          <t>3461905</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,47 +5836,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>5094</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3384078</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3100925</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3463638</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>92,69%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>84,94%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -8162,37 +5854,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3650904</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3650904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3650904</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8226,41 +5918,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>5349</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3650904</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3650904</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3650904</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8274,14 +5931,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P1435-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1435-Habitat-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>19374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39371</t>
+          <t>39323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>648980</t>
+          <t>649028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669247</t>
+          <t>668977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>648980</t>
+          <t>649028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669247</t>
+          <t>668977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>35836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63077</t>
+          <t>64666</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>35836</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63077</t>
+          <t>64666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>905316</t>
+          <t>903727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>932074</t>
+          <t>932557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>905316</t>
+          <t>903727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>932074</t>
+          <t>932557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66546</t>
+          <t>66098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99958</t>
+          <t>98739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66546</t>
+          <t>66098</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99958</t>
+          <t>98739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>583883</t>
+          <t>585102</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617295</t>
+          <t>617743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>583883</t>
+          <t>585102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>617295</t>
+          <t>617743</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84883</t>
+          <t>83378</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123458</t>
+          <t>120444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84883</t>
+          <t>83378</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123458</t>
+          <t>120444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915154</t>
+          <t>918168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>953729</t>
+          <t>955234</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>915154</t>
+          <t>918168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>953729</t>
+          <t>955234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>231258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290809</t>
+          <t>290641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229865</t>
+          <t>231258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>290809</t>
+          <t>290641</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3088388</t>
+          <t>3088556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3149332</t>
+          <t>3147939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3088388</t>
+          <t>3088556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3149332</t>
+          <t>3147939</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35250</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35250</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661800</t>
+          <t>661763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>681230</t>
+          <t>681345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>661800</t>
+          <t>661763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>681230</t>
+          <t>681345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23798</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48111</t>
+          <t>47825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23798</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48111</t>
+          <t>47825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>980862</t>
+          <t>981148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1005175</t>
+          <t>1004124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>980862</t>
+          <t>981148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1005175</t>
+          <t>1004124</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57459</t>
+          <t>57512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57459</t>
+          <t>57512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>719715</t>
+          <t>719662</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>745618</t>
+          <t>745648</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>719715</t>
+          <t>719662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>745618</t>
+          <t>745648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>25603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50707</t>
+          <t>50005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>25603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50707</t>
+          <t>50005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1001194</t>
+          <t>1001896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026246</t>
+          <t>1026298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1001194</t>
+          <t>1001896</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1026246</t>
+          <t>1026298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>162900</t>
+          <t>162178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116982</t>
+          <t>115776</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>162900</t>
+          <t>162178</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3392198</t>
+          <t>3392920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3438116</t>
+          <t>3439322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3392198</t>
+          <t>3392920</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3438116</t>
+          <t>3439322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -3395,12 +3395,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15547</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15547</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3473,12 +3473,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>657292</t>
+          <t>656976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668621</t>
+          <t>668680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>657292</t>
+          <t>656976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>668621</t>
+          <t>668680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1025051</t>
+          <t>1024572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1037406</t>
+          <t>1037403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1025051</t>
+          <t>1024572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1037406</t>
+          <t>1037403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21518</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21518</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3949,12 +3949,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>763493</t>
+          <t>763078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>778237</t>
+          <t>777331</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>763493</t>
+          <t>763078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>778237</t>
+          <t>777331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23644</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>997372</t>
+          <t>996331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1020135</t>
+          <t>1020305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>997372</t>
+          <t>996331</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1020135</t>
+          <t>1020305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -4347,12 +4347,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84756</t>
+          <t>83952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84756</t>
+          <t>83952</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3459786</t>
+          <t>3460590</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3491711</t>
+          <t>3492775</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3459786</t>
+          <t>3460590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3491711</t>
+          <t>3492775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4751,32 +4751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>31424</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41461</t>
+          <t>45448</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4786,32 +4786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>31424</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19860</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41461</t>
+          <t>45448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -4829,32 +4829,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>646745</t>
+          <t>701298</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>633909</t>
+          <t>687274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>655510</t>
+          <t>711588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4864,32 +4864,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>646745</t>
+          <t>701298</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>633909</t>
+          <t>687274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655510</t>
+          <t>711588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4907,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4989,32 +4989,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>45980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67201</t>
+          <t>73882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5024,32 +5024,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52962</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40478</t>
+          <t>45980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67201</t>
+          <t>73882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -5067,32 +5067,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>901772</t>
+          <t>1008955</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>887533</t>
+          <t>993617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>914256</t>
+          <t>1021519</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5102,32 +5102,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>901772</t>
+          <t>1008955</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>887533</t>
+          <t>993617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>914256</t>
+          <t>1021519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -5145,17 +5145,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>954734</t>
+          <t>1067499</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>954734</t>
+          <t>1067499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>954734</t>
+          <t>1067499</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>954734</t>
+          <t>1067499</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>954734</t>
+          <t>1067499</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>954734</t>
+          <t>1067499</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5227,67 +5227,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54074</t>
+          <t>68492</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27480</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78840</t>
+          <t>86864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>68492</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52117</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>86864</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
           <t>8,48%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>54074</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27480</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>78840</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -5305,67 +5305,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>875602</t>
+          <t>739451</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>850836</t>
+          <t>721079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>902196</t>
+          <t>755826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>89,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>739451</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>721079</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>755826</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>91,52%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>875602</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>850836</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>902196</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -5383,17 +5383,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>929676</t>
+          <t>807943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>929676</t>
+          <t>807943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>929676</t>
+          <t>807943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>929676</t>
+          <t>807943</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>929676</t>
+          <t>807943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>929676</t>
+          <t>807943</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5465,32 +5465,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>131165</t>
+          <t>70473</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61349</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>330793</t>
+          <t>87768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5500,32 +5500,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>131165</t>
+          <t>70473</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61349</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>330793</t>
+          <t>87768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -5543,32 +5543,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>959958</t>
+          <t>1045015</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>1027720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1029774</t>
+          <t>1059782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5578,32 +5578,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>959958</t>
+          <t>1045015</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>1027720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029774</t>
+          <t>1059782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -5621,17 +5621,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1091123</t>
+          <t>1115488</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1091123</t>
+          <t>1115488</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1091123</t>
+          <t>1115488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091123</t>
+          <t>1115488</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091123</t>
+          <t>1115488</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091123</t>
+          <t>1115488</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5703,32 +5703,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>201079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>510642</t>
+          <t>259341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5738,32 +5738,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>266826</t>
+          <t>228933</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>188999</t>
+          <t>201079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>510642</t>
+          <t>259341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -5781,32 +5781,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3384078</t>
+          <t>3494719</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3140262</t>
+          <t>3464311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3461905</t>
+          <t>3522573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3384078</t>
+          <t>3494719</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3140262</t>
+          <t>3464311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3461905</t>
+          <t>3522573</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3650904</t>
+          <t>3723652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
